--- a/productos/gafas-sol-nombres-codigos-barras.xlsx
+++ b/productos/gafas-sol-nombres-codigos-barras.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -450,154 +450,118 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Gafas de sol para niños - Azul rey</t>
+          <t>Gafas de sol para niños - Azul cielo</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2001001000011</t>
+          <t>2001001000028</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Gafas de sol para niños - Azul cielo</t>
+          <t>Gafas de sol para niños - Amarillo</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2001001000028</t>
+          <t>2001001000035</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Gafas de sol para niños - Amarillo</t>
+          <t>Gafas de sol para niños - Naranja</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>2001001000035</t>
+          <t>2001001000042</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Gafas de sol para niños - Naranja</t>
+          <t>Gafas de sol para niños - Fucsia</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>2001001000042</t>
+          <t>2001001000059</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Gafas de sol para niños - Fucsia</t>
+          <t>Gafas de sol para niños - Rosado</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>2001001000059</t>
+          <t>2001001000066</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Gafas de sol para niños - Rosado</t>
+          <t>Gafas de sol para niños - Lavanda</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>2001001000066</t>
+          <t>2001001000073</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Gafas de sol para niños - Lavanda</t>
+          <t>Gafas de sol para niños - Cuadros beige</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>2001001000073</t>
+          <t>2001001000080</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Gafas de sol para niños - Cuadros beige</t>
+          <t>Gafas de sol para niños - Cuadros azul y amarillo</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>2001001000080</t>
+          <t>2001001000097</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Gafas de sol para niños - Cuadros azul y amarillo</t>
+          <t>Gafas de sol para niños - Rayas naranja</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>2001001000097</t>
+          <t>2001001000103</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Gafas de sol para niños - Rayas naranja 1</t>
+          <t>Gafas de sol para niños - Cuadros verde</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>2001001000103</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Gafas de sol para niños - Rayas naranja 2</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>2001001000110</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Gafas de sol para niños - Rayas naranja 3</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>2001001000127</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Gafas de sol para niños - Cuadros verde</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>2001001000134</t>
         </is>
